--- a/data/trans_dic/P16A04-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A04-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,96</t>
+          <t>3,13; 9,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,82</t>
+          <t>0,42; 3,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,43</t>
+          <t>1,19; 5,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 10,89</t>
+          <t>4,38; 10,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,05</t>
+          <t>1,43; 5,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,46</t>
+          <t>1,02; 5,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,71</t>
+          <t>0,75; 3,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 9,08</t>
+          <t>4,36; 9,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,81</t>
+          <t>1,13; 3,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,81</t>
+          <t>0,62; 2,71</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,45</t>
+          <t>0,43; 2,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,22</t>
+          <t>0,82; 3,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,37</t>
+          <t>0,86; 3,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,42</t>
+          <t>0,55; 3,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,96</t>
+          <t>1,89; 4,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,66</t>
+          <t>0,6; 2,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,83</t>
+          <t>0,58; 2,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,47</t>
+          <t>1,32; 3,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,15</t>
+          <t>1,37; 3,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,79</t>
+          <t>0,94; 2,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,58</t>
+          <t>0,97; 2,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,75</t>
+          <t>1,21; 2,77</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,31</t>
+          <t>0,32; 3,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,43</t>
+          <t>1,17; 4,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,75</t>
+          <t>2,91; 7,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,33</t>
+          <t>0,27; 2,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,47</t>
+          <t>1,14; 4,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,73</t>
+          <t>0,83; 3,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 7,36</t>
+          <t>3,31; 6,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,47</t>
+          <t>0,14; 1,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,98</t>
+          <t>1,02; 2,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,57</t>
+          <t>1,27; 3,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,72</t>
+          <t>3,57; 6,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,6</t>
+          <t>0,79; 3,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,14</t>
+          <t>1,5; 5,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,69</t>
+          <t>1,18; 4,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,95</t>
+          <t>0,05; 3,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,51</t>
+          <t>1,77; 5,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,19</t>
+          <t>1,48; 5,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,9</t>
+          <t>1,28; 5,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,37</t>
+          <t>0,42; 2,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,81</t>
+          <t>1,52; 3,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,77</t>
+          <t>1,9; 4,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,99</t>
+          <t>1,49; 3,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,14</t>
+          <t>0,48; 2,14</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 9,67</t>
+          <t>2,29; 10,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,59</t>
+          <t>0,45; 4,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,81</t>
+          <t>0,92; 5,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,41</t>
+          <t>2,59; 9,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,29</t>
+          <t>1,39; 6,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,0</t>
+          <t>1,26; 3,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,23</t>
+          <t>0,68; 3,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,45</t>
+          <t>2,91; 7,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,02</t>
+          <t>1,17; 4,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,65</t>
+          <t>0,95; 2,7</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,55</t>
+          <t>0,37; 3,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,44</t>
+          <t>0,35; 3,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,31</t>
+          <t>0,36; 3,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,33</t>
+          <t>2,72; 7,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,14</t>
+          <t>0,87; 5,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,21</t>
+          <t>0,34; 3,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,7</t>
+          <t>0,32; 2,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,26</t>
+          <t>2,95; 7,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,35</t>
+          <t>0,96; 3,31</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,83</t>
+          <t>0,53; 2,91</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,31</t>
+          <t>0,5; 2,41</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,21</t>
+          <t>3,24; 6,46</t>
         </is>
       </c>
     </row>
@@ -1562,57 +1562,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,72</t>
+          <t>0,75; 2,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,91</t>
+          <t>1,95; 5,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,78</t>
+          <t>3,07; 7,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,89</t>
+          <t>0,33; 2,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,31</t>
+          <t>1,0; 3,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,46</t>
+          <t>1,65; 4,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,21</t>
+          <t>2,21; 7,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,11</t>
+          <t>0,79; 2,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,62</t>
+          <t>1,1; 2,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,31</t>
+          <t>2,19; 4,16</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,24</t>
+          <t>3,04; 6,24</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,54</t>
+          <t>2,59; 5,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,89</t>
+          <t>2,6; 5,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,35</t>
+          <t>0,69; 2,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,61</t>
+          <t>0,15; 1,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,86</t>
+          <t>1,45; 3,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,72</t>
+          <t>2,06; 4,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,61</t>
+          <t>1,35; 3,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,55</t>
+          <t>0,69; 4,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,2</t>
+          <t>2,34; 4,18</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,69</t>
+          <t>2,62; 4,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,53</t>
+          <t>1,24; 2,58</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,42</t>
+          <t>0,5; 2,34</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,28</t>
+          <t>1,38; 2,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,48</t>
+          <t>2,25; 3,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,59</t>
+          <t>1,57; 2,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,82</t>
+          <t>1,56; 2,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,77</t>
+          <t>1,75; 2,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,52</t>
+          <t>2,28; 3,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,89</t>
+          <t>1,8; 2,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 3,73</t>
+          <t>2,49; 3,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,38</t>
+          <t>1,69; 2,33</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 3,29</t>
+          <t>2,43; 3,28</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,56</t>
+          <t>1,82; 2,55</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,08</t>
+          <t>2,17; 3,04</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4905</t>
+          <t>0; 5025</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8764; 25992</t>
+          <t>9083; 27043</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1231; 11228</t>
+          <t>1237; 11115</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5240</t>
+          <t>0; 5626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3044; 14164</t>
+          <t>3117; 14158</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12662; 30630</t>
+          <t>12327; 30361</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3940; 17461</t>
+          <t>4142; 16840</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3297; 15827</t>
+          <t>2942; 15285</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3120; 14470</t>
+          <t>3997; 16000</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25479; 51910</t>
+          <t>24901; 51547</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7335; 22182</t>
+          <t>6600; 22034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3750; 16865</t>
+          <t>3721; 16260</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1940; 12083</t>
+          <t>2128; 13486</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3882; 21272</t>
+          <t>4129; 19944</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5096; 16962</t>
+          <t>4347; 17889</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2797; 17692</t>
+          <t>2850; 17459</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8762; 24975</t>
+          <t>9521; 24479</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3099; 13914</t>
+          <t>3133; 14538</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3092; 14796</t>
+          <t>3009; 14096</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6810; 17812</t>
+          <t>6799; 17367</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13165; 31356</t>
+          <t>13621; 31852</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9428; 28624</t>
+          <t>9618; 28886</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10099; 26411</t>
+          <t>9947; 26606</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11789; 28359</t>
+          <t>12497; 28563</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5743</t>
+          <t>0; 5379</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1017; 10707</t>
+          <t>1020; 10214</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3667; 14097</t>
+          <t>3716; 14908</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8854; 24443</t>
+          <t>9177; 23638</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>922; 7799</t>
+          <t>922; 7911</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3851; 15251</t>
+          <t>3886; 15287</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2801; 12542</t>
+          <t>2796; 12570</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11667; 25697</t>
+          <t>11547; 24339</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>950; 9594</t>
+          <t>945; 8716</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6844; 19811</t>
+          <t>6756; 19816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8372; 23366</t>
+          <t>8308; 22493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23460; 44674</t>
+          <t>23721; 43867</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2839; 12908</t>
+          <t>2847; 13282</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6448; 22960</t>
+          <t>5596; 21994</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4821; 17349</t>
+          <t>4365; 16382</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>317; 12341</t>
+          <t>170; 11525</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6572; 20480</t>
+          <t>6584; 19917</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5751; 20141</t>
+          <t>5725; 20854</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4635; 18983</t>
+          <t>4965; 19842</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2156; 11270</t>
+          <t>2019; 11436</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11524; 27801</t>
+          <t>11063; 27771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14966; 36373</t>
+          <t>14439; 35429</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12063; 30217</t>
+          <t>11295; 29871</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3971; 16875</t>
+          <t>3752; 16893</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4250</t>
+          <t>0; 5477</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4774; 20566</t>
+          <t>4866; 21297</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>949; 9701</t>
+          <t>942; 10040</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4100</t>
+          <t>0; 5278</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1936; 12065</t>
+          <t>1910; 11056</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5951; 20575</t>
+          <t>5657; 19854</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2280; 13748</t>
+          <t>3040; 13937</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2496; 8353</t>
+          <t>2625; 7992</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2705; 13262</t>
+          <t>2789; 13583</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13068; 36417</t>
+          <t>12543; 33571</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4614; 17273</t>
+          <t>5011; 18845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3269; 10270</t>
+          <t>3674; 10474</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>983; 9611</t>
+          <t>1007; 8647</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>984; 9425</t>
+          <t>955; 9608</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>925; 8704</t>
+          <t>940; 9471</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7621; 19760</t>
+          <t>7336; 18864</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2410; 14307</t>
+          <t>2424; 15152</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>977; 11752</t>
+          <t>958; 11099</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>869; 7371</t>
+          <t>873; 7704</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7320; 18666</t>
+          <t>7594; 18805</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5386; 18408</t>
+          <t>5250; 18152</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3639; 15661</t>
+          <t>2910; 16108</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2623; 12407</t>
+          <t>2686; 12927</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17260; 32722</t>
+          <t>17080; 34033</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5520; 19630</t>
+          <t>5550; 19623</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4841; 17937</t>
+          <t>4943; 18193</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12883; 32265</t>
+          <t>12771; 33585</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18644; 42325</t>
+          <t>19148; 44036</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2037; 12041</t>
+          <t>2087; 13270</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7231; 22936</t>
+          <t>6944; 22405</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10974; 30844</t>
+          <t>11383; 30112</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>20691; 61267</t>
+          <t>18777; 62545</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9421; 26383</t>
+          <t>9874; 26907</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14104; 35424</t>
+          <t>14957; 36124</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29025; 58140</t>
+          <t>29499; 56124</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>45452; 91969</t>
+          <t>44733; 91967</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19404; 41155</t>
+          <t>19267; 40097</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20520; 45766</t>
+          <t>20173; 43626</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4850; 18313</t>
+          <t>5397; 18737</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1396; 14918</t>
+          <t>1389; 16624</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11428; 30221</t>
+          <t>11384; 30661</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16816; 38749</t>
+          <t>16946; 39916</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11378; 29810</t>
+          <t>11152; 29626</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4952; 32505</t>
+          <t>4942; 34378</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>35696; 64166</t>
+          <t>35698; 63830</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>43263; 74933</t>
+          <t>41897; 74260</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18511; 40553</t>
+          <t>19885; 41468</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8732; 39745</t>
+          <t>8228; 38471</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>45782; 74568</t>
+          <t>45311; 75059</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>73191; 118752</t>
+          <t>76700; 118937</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53948; 87983</t>
+          <t>53214; 86710</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56889; 97638</t>
+          <t>54005; 97118</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>58066; 93580</t>
+          <t>59272; 93543</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83466; 124986</t>
+          <t>80717; 122792</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>63427; 102289</t>
+          <t>63836; 101231</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>88403; 136558</t>
+          <t>91030; 136067</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>112047; 158487</t>
+          <t>112191; 155307</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>168636; 229140</t>
+          <t>168871; 228183</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>124314; 177422</t>
+          <t>126017; 177249</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>157336; 219395</t>
+          <t>154438; 216564</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A04-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A04-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 9,32</t>
+          <t>3,25; 9,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,78</t>
+          <t>0,42; 3,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,43</t>
+          <t>1,17; 5,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,79</t>
+          <t>4,37; 10,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,83</t>
+          <t>1,37; 6,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,28</t>
+          <t>1,32; 5,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,0</t>
+          <t>0,59; 2,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 9,02</t>
+          <t>4,61; 9,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,78</t>
+          <t>1,28; 3,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,71</t>
+          <t>0,79; 2,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,74</t>
+          <t>0,43; 2,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,95</t>
+          <t>0,78; 3,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,56</t>
+          <t>0,85; 3,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,37</t>
+          <t>0,52; 3,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,86</t>
+          <t>1,75; 4,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,78</t>
+          <t>0,6; 2,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,69</t>
+          <t>0,57; 2,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,38</t>
+          <t>1,21; 3,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,19</t>
+          <t>1,31; 3,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,81</t>
+          <t>0,91; 2,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,59</t>
+          <t>0,93; 2,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,77</t>
+          <t>1,18; 2,86</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,16</t>
+          <t>0,31; 3,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,68</t>
+          <t>0,93; 4,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,49</t>
+          <t>2,5; 7,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,36</t>
+          <t>0,28; 2,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,48</t>
+          <t>1,14; 4,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,74</t>
+          <t>0,84; 3,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,97</t>
+          <t>3,43; 7,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,33</t>
+          <t>0,15; 1,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,98</t>
+          <t>1,05; 3,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,43</t>
+          <t>1,28; 3,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,6</t>
+          <t>3,46; 6,35</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,7</t>
+          <t>0,79; 3,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,88</t>
+          <t>1,52; 6,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,43</t>
+          <t>1,12; 4,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,69</t>
+          <t>0,4; 4,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,36</t>
+          <t>1,77; 5,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,38</t>
+          <t>1,47; 5,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,12</t>
+          <t>1,24; 4,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,41</t>
+          <t>0,78; 3,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,8</t>
+          <t>1,6; 3,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,65</t>
+          <t>1,95; 4,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,94</t>
+          <t>1,55; 4,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,14</t>
+          <t>0,78; 3,04</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 10,02</t>
+          <t>2,36; 10,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,75</t>
+          <t>0,45; 4,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,32</t>
+          <t>0,93; 5,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 9,08</t>
+          <t>2,32; 8,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,38</t>
+          <t>1,02; 6,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,83</t>
+          <t>1,1; 3,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,31</t>
+          <t>0,52; 2,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,79</t>
+          <t>3,07; 7,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,38</t>
+          <t>1,07; 4,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,7</t>
+          <t>0,89; 2,55</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,19</t>
+          <t>0,36; 3,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,51</t>
+          <t>0,36; 3,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,6</t>
+          <t>0,36; 3,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,0</t>
+          <t>2,65; 6,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,45</t>
+          <t>1,14; 5,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,98</t>
+          <t>0,35; 4,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,82</t>
+          <t>0,32; 3,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,32</t>
+          <t>2,94; 7,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,31</t>
+          <t>1,03; 3,57</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,91</t>
+          <t>0,53; 2,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,41</t>
+          <t>0,5; 2,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,46</t>
+          <t>3,24; 6,23</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,19</t>
+          <t>0,9; 3,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,75</t>
+          <t>0,7; 2,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,12</t>
+          <t>1,99; 5,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 7,05</t>
+          <t>3,16; 6,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,08</t>
+          <t>0,3; 1,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,23</t>
+          <t>1,01; 3,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,36</t>
+          <t>1,62; 4,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 7,36</t>
+          <t>5,48; 8,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,15</t>
+          <t>0,79; 2,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,67</t>
+          <t>1,13; 2,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,16</t>
+          <t>2,12; 4,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,24</t>
+          <t>4,86; 7,25</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,4</t>
+          <t>2,61; 5,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,61</t>
+          <t>2,61; 5,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,41</t>
+          <t>0,64; 2,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,79</t>
+          <t>0,23; 2,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,91</t>
+          <t>1,4; 3,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,86</t>
+          <t>2,13; 4,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,59</t>
+          <t>1,33; 3,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,81</t>
+          <t>0,48; 1,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,18</t>
+          <t>2,32; 4,14</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,65</t>
+          <t>2,72; 4,78</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,58</t>
+          <t>1,22; 2,52</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,34</t>
+          <t>0,52; 1,49</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,29</t>
+          <t>1,4; 2,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,48</t>
+          <t>2,28; 3,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,55</t>
+          <t>1,6; 2,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,81</t>
+          <t>1,81; 2,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,77</t>
+          <t>1,7; 2,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,46</t>
+          <t>2,37; 3,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,86</t>
+          <t>1,79; 2,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,72</t>
+          <t>2,82; 3,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,33</t>
+          <t>1,69; 2,39</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,28</t>
+          <t>2,43; 3,31</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,55</t>
+          <t>1,83; 2,59</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,04</t>
+          <t>2,51; 3,26</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>9354</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5025</t>
+          <t>0; 5579</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9083; 27043</t>
+          <t>9424; 27087</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1237; 11115</t>
+          <t>1227; 10391</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5626</t>
+          <t>0; 4400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3117; 14158</t>
+          <t>3049; 14043</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12327; 30361</t>
+          <t>12309; 30905</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4142; 16840</t>
+          <t>3968; 17519</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2942; 15285</t>
+          <t>4177; 16562</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3997; 16000</t>
+          <t>3143; 14459</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24901; 51547</t>
+          <t>26364; 51976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6600; 22034</t>
+          <t>7465; 22977</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3721; 16260</t>
+          <t>5029; 17265</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19395</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2128; 13486</t>
+          <t>2116; 12613</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4129; 19944</t>
+          <t>3955; 19877</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4347; 17889</t>
+          <t>4296; 17041</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2850; 17459</t>
+          <t>2780; 16445</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9521; 24479</t>
+          <t>8815; 24400</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3133; 14538</t>
+          <t>3150; 14751</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3009; 14096</t>
+          <t>2962; 14154</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6799; 17367</t>
+          <t>6595; 17661</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13621; 31852</t>
+          <t>13062; 30787</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9618; 28886</t>
+          <t>9369; 28034</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9947; 26606</t>
+          <t>9581; 25985</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12497; 28563</t>
+          <t>12700; 30786</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17077</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32134</t>
+          <t>31992</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5379</t>
+          <t>0; 5233</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1020; 10214</t>
+          <t>1015; 9743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3716; 14908</t>
+          <t>2949; 14240</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9177; 23638</t>
+          <t>7899; 22288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>922; 7911</t>
+          <t>926; 8255</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3886; 15287</t>
+          <t>3878; 14814</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2796; 12570</t>
+          <t>2826; 13317</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11547; 24339</t>
+          <t>12230; 25556</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>945; 8716</t>
+          <t>977; 9627</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6756; 19816</t>
+          <t>6968; 20390</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8308; 22493</t>
+          <t>8394; 23186</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23721; 43867</t>
+          <t>23219; 42646</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>12131</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2847; 13282</t>
+          <t>2847; 12714</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5596; 21994</t>
+          <t>5689; 22799</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4365; 16382</t>
+          <t>4135; 17649</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>170; 11525</t>
+          <t>1482; 15044</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6584; 19917</t>
+          <t>6572; 20340</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5725; 20854</t>
+          <t>5697; 20715</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4965; 19842</t>
+          <t>4809; 18762</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2019; 11436</t>
+          <t>3297; 16796</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11063; 27771</t>
+          <t>11716; 28879</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14439; 35429</t>
+          <t>14845; 36605</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11295; 29871</t>
+          <t>11751; 30519</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3752; 16893</t>
+          <t>6235; 24138</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6484</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5477</t>
+          <t>0; 5395</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4866; 21297</t>
+          <t>5025; 21582</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>942; 10040</t>
+          <t>946; 10066</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5278</t>
+          <t>0; 5393</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1910; 11056</t>
+          <t>1938; 11878</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5657; 19854</t>
+          <t>5080; 18707</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3040; 13937</t>
+          <t>2234; 14065</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2625; 7992</t>
+          <t>2504; 8440</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2789; 13583</t>
+          <t>2123; 11753</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12543; 33571</t>
+          <t>13220; 33801</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5011; 18845</t>
+          <t>4614; 18512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3674; 10474</t>
+          <t>3855; 11028</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>11878</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>24076</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1007; 8647</t>
+          <t>974; 9756</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>955; 9608</t>
+          <t>976; 8780</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>940; 9471</t>
+          <t>959; 9139</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7336; 18864</t>
+          <t>7168; 18884</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2424; 15152</t>
+          <t>3175; 14830</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>958; 11099</t>
+          <t>979; 11899</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>873; 7704</t>
+          <t>864; 8231</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7594; 18805</t>
+          <t>7747; 19398</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5250; 18152</t>
+          <t>5630; 19615</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2910; 16108</t>
+          <t>2919; 15311</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2686; 12927</t>
+          <t>2690; 11919</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17080; 34033</t>
+          <t>17320; 33287</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29040</t>
+          <t>34562</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>42709</t>
+          <t>54220</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71749</t>
+          <t>88782</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5550; 19623</t>
+          <t>5512; 19383</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4943; 18193</t>
+          <t>4622; 19143</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12771; 33585</t>
+          <t>13037; 33429</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19148; 44036</t>
+          <t>22745; 49130</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2087; 13270</t>
+          <t>1940; 11681</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6944; 22405</t>
+          <t>6983; 22872</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11383; 30112</t>
+          <t>11177; 30445</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18777; 62545</t>
+          <t>42344; 67419</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9874; 26907</t>
+          <t>9849; 26183</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14957; 36124</t>
+          <t>15350; 36132</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29499; 56124</t>
+          <t>28632; 54664</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>44733; 91967</t>
+          <t>72520; 108152</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>14075</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19267; 40097</t>
+          <t>19420; 40618</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20173; 43626</t>
+          <t>20258; 43270</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5397; 18737</t>
+          <t>4980; 18860</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1389; 16624</t>
+          <t>1866; 16295</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11384; 30661</t>
+          <t>10975; 28729</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16946; 39916</t>
+          <t>17521; 40078</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11152; 29626</t>
+          <t>10988; 28784</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4942; 34378</t>
+          <t>4017; 13435</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>35698; 63830</t>
+          <t>35344; 63152</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>41897; 74260</t>
+          <t>43405; 76425</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19885; 41468</t>
+          <t>19637; 40425</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8228; 38471</t>
+          <t>8426; 24189</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>75194</t>
+          <t>82148</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>111657</t>
+          <t>124142</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>186852</t>
+          <t>206290</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>45311; 75059</t>
+          <t>45808; 76703</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>76700; 118937</t>
+          <t>77743; 121968</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53214; 86710</t>
+          <t>54463; 88587</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54005; 97118</t>
+          <t>64087; 104513</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>59272; 93543</t>
+          <t>57529; 93713</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80717; 122792</t>
+          <t>83879; 124616</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>63836; 101231</t>
+          <t>63356; 101368</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>91030; 136067</t>
+          <t>105311; 144065</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>112191; 155307</t>
+          <t>112708; 159284</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>168871; 228183</t>
+          <t>168997; 230362</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>126017; 177249</t>
+          <t>126736; 179493</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>154438; 216564</t>
+          <t>182214; 236764</t>
         </is>
       </c>
     </row>
